--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HJ78"/>
+  <dimension ref="A1:HJ79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -44446,6 +44446,595 @@
         <v>104.9</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>116.45</v>
+      </c>
+      <c r="J79" t="n">
+        <v>131.607</v>
+      </c>
+      <c r="K79" t="n">
+        <v>123.55</v>
+      </c>
+      <c r="L79" t="n">
+        <v>148.588</v>
+      </c>
+      <c r="M79" t="n">
+        <v>134.46</v>
+      </c>
+      <c r="N79" t="n">
+        <v>126.45</v>
+      </c>
+      <c r="O79" t="n">
+        <v>127.75</v>
+      </c>
+      <c r="P79" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="S79" t="n">
+        <v>172.9</v>
+      </c>
+      <c r="T79" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="U79" t="n">
+        <v>224.95</v>
+      </c>
+      <c r="V79" t="n">
+        <v>124.15</v>
+      </c>
+      <c r="W79" t="n">
+        <v>399.55</v>
+      </c>
+      <c r="X79" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>279.5</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>354.25</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>96</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>90.84</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>117.25</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>110</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>150420</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>146400</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>125990</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>94.68000000000001</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>54.42</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>55.57</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>77.95</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>69.42</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>53.87</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>55.84</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>76.12</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>80.18000000000001</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>70.70999999999999</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>64.73999999999999</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>104</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>104</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>93.27</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>92.62</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>93.23999999999999</v>
+      </c>
+      <c r="BK79" t="n">
+        <v>145850</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="BR79" t="n">
+        <v>118610</v>
+      </c>
+      <c r="BS79" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>86.93000000000001</v>
+      </c>
+      <c r="BU79" t="n">
+        <v>83.75</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>108</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>90.20000000000002</v>
+      </c>
+      <c r="CB79" t="n">
+        <v>121.55</v>
+      </c>
+      <c r="CC79" t="n">
+        <v>125.285</v>
+      </c>
+      <c r="CE79" t="n">
+        <v>116.47</v>
+      </c>
+      <c r="CF79" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="CG79" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="CH79" t="n">
+        <v>46.1374</v>
+      </c>
+      <c r="CI79" t="n">
+        <v>63.4389</v>
+      </c>
+      <c r="CJ79" t="n">
+        <v>105.7316</v>
+      </c>
+      <c r="CK79" t="n">
+        <v>98</v>
+      </c>
+      <c r="CL79" t="n">
+        <v>101.1178</v>
+      </c>
+      <c r="CM79" t="n">
+        <v>98.54999999999998</v>
+      </c>
+      <c r="CN79" t="n">
+        <v>99.8202</v>
+      </c>
+      <c r="CO79" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="CP79" t="n">
+        <v>72.6664</v>
+      </c>
+      <c r="CQ79" t="n">
+        <v>105.8277</v>
+      </c>
+      <c r="CR79" t="n">
+        <v>103.8572</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="CU79" t="n">
+        <v>101</v>
+      </c>
+      <c r="CV79" t="n">
+        <v>78.83</v>
+      </c>
+      <c r="CW79" t="n">
+        <v>49.2132</v>
+      </c>
+      <c r="CX79" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="CY79" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="CZ79" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="DA79" t="n">
+        <v>104.0014</v>
+      </c>
+      <c r="DB79" t="n">
+        <v>104.482</v>
+      </c>
+      <c r="DC79" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="DD79" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="DE79" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="DF79" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="DG79" t="n">
+        <v>97</v>
+      </c>
+      <c r="DH79" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="DI79" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="DJ79" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="DK79" t="n">
+        <v>106.5967</v>
+      </c>
+      <c r="DL79" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="DM79" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="DN79" t="n">
+        <v>103.9534</v>
+      </c>
+      <c r="DO79" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="DP79" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="DQ79" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="DR79" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="DS79" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="DT79" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DU79" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="DV79" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="DW79" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="DX79" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="DY79" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="DZ79" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="EA79" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="EB79" t="n">
+        <v>103</v>
+      </c>
+      <c r="EC79" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="ED79" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EE79" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="EF79" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="EG79" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="EH79" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="EI79" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="EJ79" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="EK79" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="EL79" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="EM79" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="EN79" t="n">
+        <v>108</v>
+      </c>
+      <c r="EQ79" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="ER79" t="n">
+        <v>104</v>
+      </c>
+      <c r="ES79" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="EU79" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="EV79" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="EW79" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EX79" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="EY79" t="n">
+        <v>102.9922</v>
+      </c>
+      <c r="EZ79" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="FA79" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="FB79" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="FC79" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="FD79" t="n">
+        <v>95.50000000000001</v>
+      </c>
+      <c r="FE79" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="FF79" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="FG79" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="FH79" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="FI79" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="FJ79" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="FK79" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="FM79" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="FN79" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="FO79" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="FP79" t="n">
+        <v>102</v>
+      </c>
+      <c r="FQ79" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="FR79" t="n">
+        <v>150000</v>
+      </c>
+      <c r="FS79" t="n">
+        <v>140630</v>
+      </c>
+      <c r="FU79" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="FV79" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="FX79" t="n">
+        <v>100.1566</v>
+      </c>
+      <c r="FY79" t="n">
+        <v>23.989</v>
+      </c>
+      <c r="FZ79" t="n">
+        <v>103.4728</v>
+      </c>
+      <c r="GA79" t="n">
+        <v>98.92</v>
+      </c>
+      <c r="GB79" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="GC79" t="n">
+        <v>100.649</v>
+      </c>
+      <c r="GD79" t="n">
+        <v>149850</v>
+      </c>
+      <c r="GE79" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="GF79" t="n">
+        <v>106</v>
+      </c>
+      <c r="GG79" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="GH79" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="GI79" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="GJ79" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="GK79" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="GL79" t="n">
+        <v>28.3553</v>
+      </c>
+      <c r="GM79" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="GN79" t="n">
+        <v>106</v>
+      </c>
+      <c r="GO79" t="n">
+        <v>1742</v>
+      </c>
+      <c r="GP79" t="n">
+        <v>1464</v>
+      </c>
+      <c r="GQ79" t="n">
+        <v>48985</v>
+      </c>
+      <c r="GR79" t="n">
+        <v>35150</v>
+      </c>
+      <c r="GS79" t="n">
+        <v>43400</v>
+      </c>
+      <c r="GT79" t="n">
+        <v>101.94</v>
+      </c>
+      <c r="GU79" t="n">
+        <v>742.5</v>
+      </c>
+      <c r="GV79" t="n">
+        <v>170.1</v>
+      </c>
+      <c r="GW79" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="GX79" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="GY79" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="GZ79" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="HA79" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="HB79" t="n">
+        <v>103</v>
+      </c>
+      <c r="HC79" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="HD79" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="HE79" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="HF79" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="HG79" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="HH79" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="HI79" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="HJ79" t="n">
+        <v>105.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HJ79"/>
+  <dimension ref="A1:HO80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1517,6 +1517,31 @@
           <t>IRCOD</t>
         </is>
       </c>
+      <c r="HK1" t="inlineStr">
+        <is>
+          <t>D30N6</t>
+        </is>
+      </c>
+      <c r="HL1" t="inlineStr">
+        <is>
+          <t>PN37D</t>
+        </is>
+      </c>
+      <c r="HM1" t="inlineStr">
+        <is>
+          <t>CP41D</t>
+        </is>
+      </c>
+      <c r="HN1" t="inlineStr">
+        <is>
+          <t>VSCUD</t>
+        </is>
+      </c>
+      <c r="HO1" t="inlineStr">
+        <is>
+          <t>BF49D</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -45035,6 +45060,595 @@
         <v>105.35</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>116.55</v>
+      </c>
+      <c r="J80" t="n">
+        <v>131.73</v>
+      </c>
+      <c r="K80" t="n">
+        <v>123.68</v>
+      </c>
+      <c r="L80" t="n">
+        <v>148.79</v>
+      </c>
+      <c r="M80" t="n">
+        <v>134.581</v>
+      </c>
+      <c r="N80" t="n">
+        <v>126.55</v>
+      </c>
+      <c r="O80" t="n">
+        <v>127.8</v>
+      </c>
+      <c r="P80" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>110.95</v>
+      </c>
+      <c r="S80" t="n">
+        <v>173.12</v>
+      </c>
+      <c r="T80" t="n">
+        <v>304.7</v>
+      </c>
+      <c r="U80" t="n">
+        <v>225.3</v>
+      </c>
+      <c r="V80" t="n">
+        <v>124.55</v>
+      </c>
+      <c r="W80" t="n">
+        <v>400.5500000000001</v>
+      </c>
+      <c r="X80" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>280.4</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>354.85</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>91.12</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>150400</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>146390</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>126120</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>94.85000000000001</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>54.37</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>92.25</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>55.63</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>70.15000000000001</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>53.94</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>55.67999999999999</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>75.58</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>79.08</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>70.42</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>64.79000000000001</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>93.15000000000002</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>92.44999999999999</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="BK80" t="n">
+        <v>146490</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>103.7008</v>
+      </c>
+      <c r="BR80" t="n">
+        <v>119100</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>94.38</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>83.75</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>105.595</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>86.39</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>90.39000000000001</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="CC80" t="n">
+        <v>125.42</v>
+      </c>
+      <c r="CE80" t="n">
+        <v>116.54</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="CH80" t="n">
+        <v>45.9452</v>
+      </c>
+      <c r="CI80" t="n">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>105.7172</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>100.6282</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="CO80" t="n">
+        <v>67.76000000000001</v>
+      </c>
+      <c r="CP80" t="n">
+        <v>72.49460000000001</v>
+      </c>
+      <c r="CQ80" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>104.2769</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="CU80" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="CV80" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="CW80" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="CX80" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="CY80" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="CZ80" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="DA80" t="n">
+        <v>103.8929</v>
+      </c>
+      <c r="DB80" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="DC80" t="n">
+        <v>102.1645</v>
+      </c>
+      <c r="DD80" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="DE80" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="DF80" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="DG80" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="DH80" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="DI80" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="DJ80" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="DK80" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="DL80" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="DM80" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="DN80" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="DO80" t="n">
+        <v>105</v>
+      </c>
+      <c r="DP80" t="n">
+        <v>91.48999999999999</v>
+      </c>
+      <c r="DQ80" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="DR80" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="DS80" t="n">
+        <v>105</v>
+      </c>
+      <c r="DT80" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="DU80" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="DV80" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="DW80" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="DX80" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="DY80" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="DZ80" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="EA80" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="EB80" t="n">
+        <v>103.5088</v>
+      </c>
+      <c r="EC80" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="ED80" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EE80" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="EF80" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="EG80" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="EH80" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="EI80" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EJ80" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="EK80" t="n">
+        <v>104</v>
+      </c>
+      <c r="EL80" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="EM80" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="EN80" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="EQ80" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="ER80" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="ES80" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="EU80" t="n">
+        <v>104</v>
+      </c>
+      <c r="EV80" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="EW80" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="EX80" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="EY80" t="n">
+        <v>103</v>
+      </c>
+      <c r="EZ80" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="FA80" t="n">
+        <v>104</v>
+      </c>
+      <c r="FB80" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="FC80" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="FD80" t="n">
+        <v>95.12</v>
+      </c>
+      <c r="FE80" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="FF80" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="FG80" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="FH80" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="FI80" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="FJ80" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="FK80" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="FM80" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="FN80" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="FQ80" t="n">
+        <v>103.32</v>
+      </c>
+      <c r="FR80" t="n">
+        <v>149990</v>
+      </c>
+      <c r="FS80" t="n">
+        <v>140790</v>
+      </c>
+      <c r="FU80" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="FV80" t="n">
+        <v>100</v>
+      </c>
+      <c r="FX80" t="n">
+        <v>100.15</v>
+      </c>
+      <c r="FY80" t="n">
+        <v>23.651</v>
+      </c>
+      <c r="FZ80" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="GA80" t="n">
+        <v>98.94</v>
+      </c>
+      <c r="GB80" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="GC80" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="GD80" t="n">
+        <v>149770</v>
+      </c>
+      <c r="GE80" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="GF80" t="n">
+        <v>106</v>
+      </c>
+      <c r="GG80" t="n">
+        <v>102</v>
+      </c>
+      <c r="GH80" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="GI80" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="GJ80" t="n">
+        <v>102</v>
+      </c>
+      <c r="GK80" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="GL80" t="n">
+        <v>26.9334</v>
+      </c>
+      <c r="GM80" t="n">
+        <v>101</v>
+      </c>
+      <c r="GN80" t="n">
+        <v>105</v>
+      </c>
+      <c r="GO80" t="n">
+        <v>1745.5</v>
+      </c>
+      <c r="GP80" t="n">
+        <v>1461</v>
+      </c>
+      <c r="GQ80" t="n">
+        <v>49000</v>
+      </c>
+      <c r="GR80" t="n">
+        <v>35060</v>
+      </c>
+      <c r="GS80" t="n">
+        <v>43075</v>
+      </c>
+      <c r="GT80" t="n">
+        <v>102.03</v>
+      </c>
+      <c r="GU80" t="n">
+        <v>743.3</v>
+      </c>
+      <c r="GV80" t="n">
+        <v>170.25</v>
+      </c>
+      <c r="GW80" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="GX80" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="GY80" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="GZ80" t="n">
+        <v>105</v>
+      </c>
+      <c r="HA80" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="HB80" t="n">
+        <v>103</v>
+      </c>
+      <c r="HC80" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="HD80" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="HE80" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="HF80" t="n">
+        <v>105.5252</v>
+      </c>
+      <c r="HG80" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="HI80" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="HJ80" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="HL80" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="HM80" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="HN80" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="HO80" t="n">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HO80"/>
+  <dimension ref="A1:HO81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -45649,6 +45649,595 @@
         <v>102</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>116.624</v>
+      </c>
+      <c r="J81" t="n">
+        <v>131.885</v>
+      </c>
+      <c r="K81" t="n">
+        <v>123.786</v>
+      </c>
+      <c r="L81" t="n">
+        <v>148.95</v>
+      </c>
+      <c r="M81" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="N81" t="n">
+        <v>126.68</v>
+      </c>
+      <c r="O81" t="n">
+        <v>127.94</v>
+      </c>
+      <c r="P81" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>111.05</v>
+      </c>
+      <c r="S81" t="n">
+        <v>173.255</v>
+      </c>
+      <c r="T81" t="n">
+        <v>305</v>
+      </c>
+      <c r="U81" t="n">
+        <v>225.95</v>
+      </c>
+      <c r="V81" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="W81" t="n">
+        <v>402.55</v>
+      </c>
+      <c r="X81" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>281</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>354.85</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>96.13</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>122.7</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>110.38</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>151050</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>145740</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>127700</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>94.78</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>92.20999999999999</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>55.50999999999999</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>74.67</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>77.20999999999999</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>69.31</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>54.24</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>55.61000000000001</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>75.63</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>79.33</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>92.79999999999998</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>93.51000000000001</v>
+      </c>
+      <c r="BK81" t="n">
+        <v>147100</v>
+      </c>
+      <c r="BM81" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="BN81" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>103.8979</v>
+      </c>
+      <c r="BR81" t="n">
+        <v>120290</v>
+      </c>
+      <c r="BS81" t="n">
+        <v>94.48999999999999</v>
+      </c>
+      <c r="BT81" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="BU81" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="BV81" t="n">
+        <v>105.685</v>
+      </c>
+      <c r="BW81" t="n">
+        <v>98.84999999999999</v>
+      </c>
+      <c r="BX81" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="BY81" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="BZ81" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA81" t="n">
+        <v>89.79000000000001</v>
+      </c>
+      <c r="CB81" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="CC81" t="n">
+        <v>125.55</v>
+      </c>
+      <c r="CE81" t="n">
+        <v>116.65</v>
+      </c>
+      <c r="CF81" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="CG81" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="CH81" t="n">
+        <v>46.1768</v>
+      </c>
+      <c r="CI81" t="n">
+        <v>62.002</v>
+      </c>
+      <c r="CJ81" t="n">
+        <v>105.8219</v>
+      </c>
+      <c r="CL81" t="n">
+        <v>100.8194</v>
+      </c>
+      <c r="CM81" t="n">
+        <v>97.6447</v>
+      </c>
+      <c r="CN81" t="n">
+        <v>100.7713</v>
+      </c>
+      <c r="CO81" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="CP81" t="n">
+        <v>72.1032</v>
+      </c>
+      <c r="CQ81" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="CR81" t="n">
+        <v>103.8017</v>
+      </c>
+      <c r="CS81" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="CT81" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="CU81" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="CV81" t="n">
+        <v>78.62</v>
+      </c>
+      <c r="CW81" t="n">
+        <v>49.2553</v>
+      </c>
+      <c r="CX81" t="n">
+        <v>108</v>
+      </c>
+      <c r="CY81" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="CZ81" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="DA81" t="n">
+        <v>104.6675</v>
+      </c>
+      <c r="DB81" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="DC81" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="DD81" t="n">
+        <v>104</v>
+      </c>
+      <c r="DE81" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="DF81" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="DG81" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="DH81" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="DI81" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="DJ81" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="DK81" t="n">
+        <v>106.3991</v>
+      </c>
+      <c r="DL81" t="n">
+        <v>104.3789</v>
+      </c>
+      <c r="DM81" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="DN81" t="n">
+        <v>103.032</v>
+      </c>
+      <c r="DO81" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="DP81" t="n">
+        <v>90.25</v>
+      </c>
+      <c r="DQ81" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="DR81" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="DS81" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="DT81" t="n">
+        <v>105.1004</v>
+      </c>
+      <c r="DU81" t="n">
+        <v>107</v>
+      </c>
+      <c r="DV81" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="DW81" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="DX81" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="DY81" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DZ81" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="EA81" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="EB81" t="n">
+        <v>103</v>
+      </c>
+      <c r="EC81" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="ED81" t="n">
+        <v>102</v>
+      </c>
+      <c r="EE81" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="EF81" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="EG81" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="EH81" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="EI81" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="EJ81" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="EK81" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="EL81" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="EM81" t="n">
+        <v>100.85</v>
+      </c>
+      <c r="EN81" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="EQ81" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="ER81" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="ES81" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="EU81" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="EV81" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="EW81" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="EX81" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="EY81" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EZ81" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="FA81" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="FB81" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="FC81" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="FD81" t="n">
+        <v>95.15000000000001</v>
+      </c>
+      <c r="FE81" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="FF81" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="FH81" t="n">
+        <v>105</v>
+      </c>
+      <c r="FI81" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="FJ81" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="FK81" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="FM81" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="FN81" t="n">
+        <v>102</v>
+      </c>
+      <c r="FQ81" t="n">
+        <v>103.39</v>
+      </c>
+      <c r="FR81" t="n">
+        <v>148800</v>
+      </c>
+      <c r="FS81" t="n">
+        <v>141280</v>
+      </c>
+      <c r="FU81" t="n">
+        <v>101</v>
+      </c>
+      <c r="FV81" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="FW81" t="n">
+        <v>98.46250000000001</v>
+      </c>
+      <c r="FX81" t="n">
+        <v>99.41</v>
+      </c>
+      <c r="FY81" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="FZ81" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="GA81" t="n">
+        <v>98.45999999999999</v>
+      </c>
+      <c r="GB81" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="GC81" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="GD81" t="n">
+        <v>150600</v>
+      </c>
+      <c r="GE81" t="n">
+        <v>110.2953</v>
+      </c>
+      <c r="GF81" t="n">
+        <v>106</v>
+      </c>
+      <c r="GG81" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="GH81" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="GI81" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="GJ81" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="GK81" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="GL81" t="n">
+        <v>27.4175</v>
+      </c>
+      <c r="GM81" t="n">
+        <v>101</v>
+      </c>
+      <c r="GN81" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="GO81" t="n">
+        <v>1760</v>
+      </c>
+      <c r="GP81" t="n">
+        <v>1453</v>
+      </c>
+      <c r="GQ81" t="n">
+        <v>48865</v>
+      </c>
+      <c r="GR81" t="n">
+        <v>34780</v>
+      </c>
+      <c r="GS81" t="n">
+        <v>43010</v>
+      </c>
+      <c r="GT81" t="n">
+        <v>102.156</v>
+      </c>
+      <c r="GU81" t="n">
+        <v>744</v>
+      </c>
+      <c r="GV81" t="n">
+        <v>170.2</v>
+      </c>
+      <c r="GW81" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="GX81" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="GY81" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="GZ81" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="HA81" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="HB81" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="HC81" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="HD81" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="HE81" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="HF81" t="n">
+        <v>105.8219</v>
+      </c>
+      <c r="HG81" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="HI81" t="n">
+        <v>102</v>
+      </c>
+      <c r="HJ81" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="HK81" t="n">
+        <v>147800</v>
+      </c>
+      <c r="HL81" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="HM81" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="HN81" t="n">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1994,6 +1994,9 @@
       <c r="HJ2" t="n">
         <v>105.35</v>
       </c>
+      <c r="HL2" t="n">
+        <v>100.6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2493,6 +2496,9 @@
       <c r="HJ3" t="n">
         <v>106.75</v>
       </c>
+      <c r="HL3" t="n">
+        <v>102.75</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2995,6 +3001,9 @@
       <c r="HJ4" t="n">
         <v>106.15</v>
       </c>
+      <c r="HL4" t="n">
+        <v>103.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3500,6 +3509,9 @@
       <c r="HJ5" t="n">
         <v>106.4</v>
       </c>
+      <c r="HL5" t="n">
+        <v>102.75</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4014,6 +4026,9 @@
       <c r="HJ6" t="n">
         <v>107</v>
       </c>
+      <c r="HL6" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4540,6 +4555,12 @@
       <c r="HJ7" t="n">
         <v>106.2</v>
       </c>
+      <c r="HL7" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="HN7" t="n">
+        <v>103.8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5060,6 +5081,9 @@
       <c r="HJ8" t="n">
         <v>105.8</v>
       </c>
+      <c r="HL8" t="n">
+        <v>102.7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5586,6 +5610,9 @@
       <c r="HJ9" t="n">
         <v>106.2</v>
       </c>
+      <c r="HL9" t="n">
+        <v>102.9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6118,6 +6145,9 @@
       <c r="HJ10" t="n">
         <v>106.9</v>
       </c>
+      <c r="HL10" t="n">
+        <v>103.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6632,6 +6662,9 @@
       <c r="HJ11" t="n">
         <v>106.85</v>
       </c>
+      <c r="HL11" t="n">
+        <v>103.4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7143,6 +7176,9 @@
       <c r="HJ12" t="n">
         <v>106.3</v>
       </c>
+      <c r="HL12" t="n">
+        <v>103.05</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7669,6 +7705,12 @@
       <c r="HJ13" t="n">
         <v>107.7</v>
       </c>
+      <c r="HL13" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="HN13" t="n">
+        <v>103.55</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8195,6 +8237,9 @@
       <c r="HJ14" t="n">
         <v>107.2</v>
       </c>
+      <c r="HL14" t="n">
+        <v>102.8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8715,6 +8760,9 @@
       <c r="HJ15" t="n">
         <v>108.5</v>
       </c>
+      <c r="HL15" t="n">
+        <v>103.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9253,6 +9301,9 @@
       <c r="HJ16" t="n">
         <v>108.45</v>
       </c>
+      <c r="HL16" t="n">
+        <v>103.65</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9788,6 +9839,9 @@
       <c r="HJ17" t="n">
         <v>107.5</v>
       </c>
+      <c r="HL17" t="n">
+        <v>103.15</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10323,6 +10377,9 @@
       <c r="HJ18" t="n">
         <v>107.15</v>
       </c>
+      <c r="HL18" t="n">
+        <v>103.75</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10858,6 +10915,9 @@
       <c r="HJ19" t="n">
         <v>106.9</v>
       </c>
+      <c r="HL19" t="n">
+        <v>103.2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11393,6 +11453,9 @@
       <c r="HJ20" t="n">
         <v>107.2</v>
       </c>
+      <c r="HL20" t="n">
+        <v>103.5</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11931,6 +11994,12 @@
       <c r="HJ21" t="n">
         <v>106.9</v>
       </c>
+      <c r="HL21" t="n">
+        <v>104</v>
+      </c>
+      <c r="HN21" t="n">
+        <v>103.7</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12484,6 +12553,12 @@
       <c r="HJ22" t="n">
         <v>107.7</v>
       </c>
+      <c r="HL22" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="HN22" t="n">
+        <v>105.95</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -13028,6 +13103,9 @@
       <c r="HJ23" t="n">
         <v>107.75</v>
       </c>
+      <c r="HL23" t="n">
+        <v>103.1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13575,6 +13653,12 @@
       <c r="HJ24" t="n">
         <v>107.8</v>
       </c>
+      <c r="HL24" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="HN24" t="n">
+        <v>106.4</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -14119,6 +14203,9 @@
       <c r="HJ25" t="n">
         <v>108.85</v>
       </c>
+      <c r="HL25" t="n">
+        <v>103.7</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -14654,6 +14741,9 @@
       <c r="HJ26" t="n">
         <v>107.75</v>
       </c>
+      <c r="HL26" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15195,6 +15285,12 @@
       <c r="HJ27" t="n">
         <v>108.35</v>
       </c>
+      <c r="HL27" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="HN27" t="n">
+        <v>106.35</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -15739,6 +15835,12 @@
       <c r="HJ28" t="n">
         <v>107.9</v>
       </c>
+      <c r="HL28" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="HN28" t="n">
+        <v>106.15</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -16292,6 +16394,12 @@
       <c r="HJ29" t="n">
         <v>108.6</v>
       </c>
+      <c r="HL29" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="HN29" t="n">
+        <v>106.95</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -16842,6 +16950,9 @@
       <c r="HJ30" t="n">
         <v>107.5</v>
       </c>
+      <c r="HL30" t="n">
+        <v>103.5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -17401,6 +17512,12 @@
       <c r="HJ31" t="n">
         <v>107.2</v>
       </c>
+      <c r="HL31" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="HN31" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -17951,6 +18068,12 @@
       <c r="HJ32" t="n">
         <v>107.4</v>
       </c>
+      <c r="HL32" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="HN32" t="n">
+        <v>106.75</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -18507,6 +18630,9 @@
       <c r="HJ33" t="n">
         <v>107.25</v>
       </c>
+      <c r="HL33" t="n">
+        <v>104.85</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -18994,6 +19120,9 @@
       <c r="HJ34" t="n">
         <v>107.5</v>
       </c>
+      <c r="HL34" t="n">
+        <v>104.95</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -19556,6 +19685,12 @@
       <c r="HJ35" t="n">
         <v>107.45</v>
       </c>
+      <c r="HL35" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="HN35" t="n">
+        <v>106.4</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -20115,6 +20250,12 @@
       <c r="HJ36" t="n">
         <v>107.7</v>
       </c>
+      <c r="HL36" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="HN36" t="n">
+        <v>105.25</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -20674,6 +20815,12 @@
       <c r="HJ37" t="n">
         <v>108</v>
       </c>
+      <c r="HL37" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="HN37" t="n">
+        <v>105.5</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -21236,6 +21383,12 @@
       <c r="HJ38" t="n">
         <v>108.1</v>
       </c>
+      <c r="HL38" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="HN38" t="n">
+        <v>105.8</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -21813,6 +21966,12 @@
       <c r="HJ39" t="n">
         <v>108.4</v>
       </c>
+      <c r="HL39" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="HN39" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -22375,6 +22534,12 @@
       <c r="HJ40" t="n">
         <v>108.1</v>
       </c>
+      <c r="HL40" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="HN40" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -22937,6 +23102,12 @@
       <c r="HJ41" t="n">
         <v>108.35</v>
       </c>
+      <c r="HL41" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="HN41" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -23502,6 +23673,12 @@
       <c r="HJ42" t="n">
         <v>106.5</v>
       </c>
+      <c r="HL42" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="HN42" t="n">
+        <v>106.8</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -24064,6 +24241,12 @@
       <c r="HJ43" t="n">
         <v>107.4</v>
       </c>
+      <c r="HL43" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="HN43" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -24644,6 +24827,12 @@
       <c r="HJ44" t="n">
         <v>106.3</v>
       </c>
+      <c r="HL44" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="HN44" t="n">
+        <v>104.85</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -25221,6 +25410,12 @@
       <c r="HJ45" t="n">
         <v>105.2</v>
       </c>
+      <c r="HL45" t="n">
+        <v>104</v>
+      </c>
+      <c r="HN45" t="n">
+        <v>106.5</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -25798,6 +25993,12 @@
       <c r="HJ46" t="n">
         <v>106.3</v>
       </c>
+      <c r="HL46" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="HO46" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -26372,6 +26573,15 @@
       <c r="HJ47" t="n">
         <v>105.4</v>
       </c>
+      <c r="HL47" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="HN47" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="HO47" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -26932,6 +27142,12 @@
       <c r="HJ48" t="n">
         <v>104.9</v>
       </c>
+      <c r="HL48" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="HO48" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -27500,6 +27716,15 @@
       </c>
       <c r="HJ49" t="n">
         <v>105.05</v>
+      </c>
+      <c r="HL49" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="HN49" t="n">
+        <v>108</v>
+      </c>
+      <c r="HO49" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="50">
@@ -28090,6 +28315,9 @@
       <c r="HJ50" t="n">
         <v>105.9</v>
       </c>
+      <c r="HL50" t="n">
+        <v>104.15</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -28670,6 +28898,9 @@
       <c r="HJ51" t="n">
         <v>105.9</v>
       </c>
+      <c r="HL51" t="n">
+        <v>104.5</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -29250,6 +29481,9 @@
       <c r="HJ52" t="n">
         <v>105.75</v>
       </c>
+      <c r="HL52" t="n">
+        <v>104.1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -29834,6 +30068,12 @@
       <c r="HJ53" t="n">
         <v>105.4</v>
       </c>
+      <c r="HL53" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="HN53" t="n">
+        <v>108.4</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -30417,6 +30657,12 @@
       </c>
       <c r="HJ54" t="n">
         <v>106.65</v>
+      </c>
+      <c r="HL54" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="HN54" t="n">
+        <v>108.4</v>
       </c>
     </row>
     <row r="55">
@@ -31001,6 +31247,12 @@
       <c r="HJ55" t="n">
         <v>105.8</v>
       </c>
+      <c r="HL55" t="n">
+        <v>104</v>
+      </c>
+      <c r="HN55" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -31590,6 +31842,12 @@
       <c r="HJ56" t="n">
         <v>105.45</v>
       </c>
+      <c r="HL56" t="n">
+        <v>104</v>
+      </c>
+      <c r="HN56" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -32170,6 +32428,9 @@
       <c r="HJ57" t="n">
         <v>104.8</v>
       </c>
+      <c r="HL57" t="n">
+        <v>104.55</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -32750,6 +33011,12 @@
       <c r="HJ58" t="n">
         <v>105.7</v>
       </c>
+      <c r="HL58" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="HN58" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -33339,6 +33606,12 @@
       <c r="HJ59" t="n">
         <v>105.4</v>
       </c>
+      <c r="HL59" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="HN59" t="n">
+        <v>106.95</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -33928,6 +34201,9 @@
       <c r="HJ60" t="n">
         <v>105.7</v>
       </c>
+      <c r="HL60" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -34520,6 +34796,12 @@
       <c r="HJ61" t="n">
         <v>105</v>
       </c>
+      <c r="HL61" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="HN61" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -35112,6 +35394,12 @@
       <c r="HJ62" t="n">
         <v>104.7</v>
       </c>
+      <c r="HL62" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="HN62" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -35704,6 +35992,9 @@
       <c r="HJ63" t="n">
         <v>104.7</v>
       </c>
+      <c r="HL63" t="n">
+        <v>104.4</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -36251,6 +36542,12 @@
       <c r="HJ64" t="n">
         <v>104.5</v>
       </c>
+      <c r="HL64" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="HN64" t="n">
+        <v>107.2</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -36849,6 +37146,12 @@
       <c r="HJ65" t="n">
         <v>104.1</v>
       </c>
+      <c r="HL65" t="n">
+        <v>104</v>
+      </c>
+      <c r="HN65" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -37438,6 +37741,9 @@
       <c r="HJ66" t="n">
         <v>104.35</v>
       </c>
+      <c r="HL66" t="n">
+        <v>103.4</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -38033,6 +38339,9 @@
       <c r="HJ67" t="n">
         <v>104</v>
       </c>
+      <c r="HL67" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -38610,6 +38919,9 @@
       <c r="HJ68" t="n">
         <v>104.9</v>
       </c>
+      <c r="HL68" t="n">
+        <v>103.9</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -39193,6 +39505,9 @@
       <c r="HJ69" t="n">
         <v>104.95</v>
       </c>
+      <c r="HL69" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -39776,6 +40091,9 @@
       <c r="HJ70" t="n">
         <v>104.9</v>
       </c>
+      <c r="HL70" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -40362,6 +40680,9 @@
       <c r="HJ71" t="n">
         <v>105</v>
       </c>
+      <c r="HL71" t="n">
+        <v>103.95</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -40948,6 +41269,15 @@
       <c r="HJ72" t="n">
         <v>105.55</v>
       </c>
+      <c r="HL72" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="HN72" t="n">
+        <v>107</v>
+      </c>
+      <c r="HO72" t="n">
+        <v>100.3</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -41534,6 +41864,9 @@
       <c r="HJ73" t="n">
         <v>105.5</v>
       </c>
+      <c r="HL73" t="n">
+        <v>103.7</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -42120,6 +42453,12 @@
       <c r="HJ74" t="n">
         <v>105.3</v>
       </c>
+      <c r="HL74" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="HM74" t="n">
+        <v>100.5</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -42709,6 +43048,15 @@
       <c r="HJ75" t="n">
         <v>104.6</v>
       </c>
+      <c r="HL75" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="HM75" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="HN75" t="n">
+        <v>103.95</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -43295,6 +43643,15 @@
       <c r="HJ76" t="n">
         <v>104.3</v>
       </c>
+      <c r="HL76" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="HM76" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="HN76" t="n">
+        <v>105.8</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -43884,6 +44241,15 @@
       <c r="HJ77" t="n">
         <v>104.8</v>
       </c>
+      <c r="HL77" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="HM77" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="HN77" t="n">
+        <v>103.2</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -44470,6 +44836,18 @@
       <c r="HJ78" t="n">
         <v>104.9</v>
       </c>
+      <c r="HL78" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="HM78" t="n">
+        <v>101</v>
+      </c>
+      <c r="HN78" t="n">
+        <v>105</v>
+      </c>
+      <c r="HO78" t="n">
+        <v>100.5</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -45059,6 +45437,18 @@
       <c r="HJ79" t="n">
         <v>105.35</v>
       </c>
+      <c r="HL79" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="HM79" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="HN79" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="HO79" t="n">
+        <v>100.5</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HO81"/>
+  <dimension ref="A1:HO82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -46628,6 +46628,601 @@
         <v>105</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>116.699</v>
+      </c>
+      <c r="J82" t="n">
+        <v>132.16</v>
+      </c>
+      <c r="K82" t="n">
+        <v>123.96</v>
+      </c>
+      <c r="L82" t="n">
+        <v>149.195</v>
+      </c>
+      <c r="M82" t="n">
+        <v>134.99</v>
+      </c>
+      <c r="N82" t="n">
+        <v>127.099</v>
+      </c>
+      <c r="O82" t="n">
+        <v>128.15</v>
+      </c>
+      <c r="P82" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>112</v>
+      </c>
+      <c r="S82" t="n">
+        <v>173.7</v>
+      </c>
+      <c r="T82" t="n">
+        <v>305.6</v>
+      </c>
+      <c r="U82" t="n">
+        <v>226.55</v>
+      </c>
+      <c r="V82" t="n">
+        <v>125</v>
+      </c>
+      <c r="W82" t="n">
+        <v>404.05</v>
+      </c>
+      <c r="X82" t="n">
+        <v>109</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>281.65</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>355.3</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>96.55</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>91</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>122.95</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>118.1</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>150760</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>145770</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>127550</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>94.79000000000001</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>54.29999999999999</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>55.58</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>74.64</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>68.69</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>53.95999999999999</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>55.66</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>75.55</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>64.91</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>93.06</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>92.99999999999999</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>101</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="BK82" t="n">
+        <v>146800</v>
+      </c>
+      <c r="BM82" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="BN82" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="BO82" t="n">
+        <v>109.05</v>
+      </c>
+      <c r="BP82" t="n">
+        <v>103.9731</v>
+      </c>
+      <c r="BR82" t="n">
+        <v>120600</v>
+      </c>
+      <c r="BS82" t="n">
+        <v>94.95</v>
+      </c>
+      <c r="BT82" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="BU82" t="n">
+        <v>84.33</v>
+      </c>
+      <c r="BV82" t="n">
+        <v>105.88</v>
+      </c>
+      <c r="BW82" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="BX82" t="n">
+        <v>86.05</v>
+      </c>
+      <c r="BY82" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="BZ82" t="n">
+        <v>150000</v>
+      </c>
+      <c r="CA82" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="CB82" t="n">
+        <v>123.25</v>
+      </c>
+      <c r="CC82" t="n">
+        <v>125.81</v>
+      </c>
+      <c r="CE82" t="n">
+        <v>116.735</v>
+      </c>
+      <c r="CF82" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="CG82" t="n">
+        <v>104</v>
+      </c>
+      <c r="CH82" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="CI82" t="n">
+        <v>62.2973</v>
+      </c>
+      <c r="CJ82" t="n">
+        <v>105.3671</v>
+      </c>
+      <c r="CK82" t="n">
+        <v>98.36</v>
+      </c>
+      <c r="CL82" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="CM82" t="n">
+        <v>98.58</v>
+      </c>
+      <c r="CN82" t="n">
+        <v>100.6563</v>
+      </c>
+      <c r="CO82" t="n">
+        <v>67.37</v>
+      </c>
+      <c r="CP82" t="n">
+        <v>72.536</v>
+      </c>
+      <c r="CQ82" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="CR82" t="n">
+        <v>104.2134</v>
+      </c>
+      <c r="CS82" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="CT82" t="n">
+        <v>105.4632</v>
+      </c>
+      <c r="CU82" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="CV82" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="CW82" t="n">
+        <v>49.3668</v>
+      </c>
+      <c r="CX82" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="CY82" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="CZ82" t="n">
+        <v>100</v>
+      </c>
+      <c r="DA82" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="DB82" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="DC82" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="DD82" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="DE82" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="DF82" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="DG82" t="n">
+        <v>99</v>
+      </c>
+      <c r="DH82" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="DI82" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="DJ82" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="DK82" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="DL82" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="DM82" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DN82" t="n">
+        <v>103.3482</v>
+      </c>
+      <c r="DO82" t="n">
+        <v>104</v>
+      </c>
+      <c r="DP82" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="DQ82" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="DR82" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="DS82" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="DT82" t="n">
+        <v>104.598</v>
+      </c>
+      <c r="DU82" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="DV82" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="DW82" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="DX82" t="n">
+        <v>102.1465</v>
+      </c>
+      <c r="DY82" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="DZ82" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="EA82" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="EB82" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EC82" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="ED82" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="EE82" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="EF82" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="EG82" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="EH82" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="EI82" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EJ82" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="EK82" t="n">
+        <v>104</v>
+      </c>
+      <c r="EL82" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="EM82" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="EN82" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="EQ82" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="ER82" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="ES82" t="n">
+        <v>102</v>
+      </c>
+      <c r="EU82" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="EV82" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="EW82" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="EX82" t="n">
+        <v>104</v>
+      </c>
+      <c r="EY82" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="EZ82" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="FA82" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="FB82" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="FC82" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="FD82" t="n">
+        <v>95.25000000000001</v>
+      </c>
+      <c r="FE82" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="FF82" t="n">
+        <v>103</v>
+      </c>
+      <c r="FG82" t="n">
+        <v>100.85</v>
+      </c>
+      <c r="FH82" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="FI82" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="FJ82" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="FK82" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="FM82" t="n">
+        <v>104</v>
+      </c>
+      <c r="FN82" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="FP82" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="FQ82" t="n">
+        <v>103.465</v>
+      </c>
+      <c r="FR82" t="n">
+        <v>148600</v>
+      </c>
+      <c r="FS82" t="n">
+        <v>142200</v>
+      </c>
+      <c r="FU82" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="FV82" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="FW82" t="n">
+        <v>98.39709999999999</v>
+      </c>
+      <c r="FX82" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="FY82" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="FZ82" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="GA82" t="n">
+        <v>98.23</v>
+      </c>
+      <c r="GB82" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="GC82" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="GD82" t="n">
+        <v>150240</v>
+      </c>
+      <c r="GE82" t="n">
+        <v>109.9336</v>
+      </c>
+      <c r="GF82" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="GG82" t="n">
+        <v>102</v>
+      </c>
+      <c r="GH82" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="GI82" t="n">
+        <v>105</v>
+      </c>
+      <c r="GJ82" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="GK82" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GM82" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="GN82" t="n">
+        <v>104.4057</v>
+      </c>
+      <c r="GO82" t="n">
+        <v>1763</v>
+      </c>
+      <c r="GP82" t="n">
+        <v>1462</v>
+      </c>
+      <c r="GQ82" t="n">
+        <v>49075</v>
+      </c>
+      <c r="GR82" t="n">
+        <v>34985</v>
+      </c>
+      <c r="GS82" t="n">
+        <v>43195</v>
+      </c>
+      <c r="GT82" t="n">
+        <v>102.43</v>
+      </c>
+      <c r="GU82" t="n">
+        <v>748.9</v>
+      </c>
+      <c r="GV82" t="n">
+        <v>170.4</v>
+      </c>
+      <c r="GW82" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="GX82" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="GY82" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="GZ82" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="HA82" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="HB82" t="n">
+        <v>102</v>
+      </c>
+      <c r="HC82" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="HD82" t="n">
+        <v>105</v>
+      </c>
+      <c r="HE82" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="HF82" t="n">
+        <v>104.1654</v>
+      </c>
+      <c r="HG82" t="n">
+        <v>99.54000000000002</v>
+      </c>
+      <c r="HI82" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="HJ82" t="n">
+        <v>106</v>
+      </c>
+      <c r="HK82" t="n">
+        <v>150590</v>
+      </c>
+      <c r="HL82" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="HM82" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="HN82" t="n">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
